--- a/doc/research/openclaw_google_trend.xlsx
+++ b/doc/research/openclaw_google_trend.xlsx
@@ -1660,7 +1660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:E189"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
@@ -1874,7 +1874,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" hidden="1" spans="1:5">
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1891,7 +1891,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" hidden="1" spans="1:5">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" hidden="1" spans="1:5">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1925,7 +1925,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" hidden="1" spans="1:5">
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" hidden="1" spans="1:5">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" hidden="1" spans="1:5">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" hidden="1" spans="1:5">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>35</v>
       </c>
@@ -1993,7 +1993,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" hidden="1" spans="1:5">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" hidden="1" spans="1:5">
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" hidden="1" spans="1:5">
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -2044,7 +2044,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" hidden="1" spans="1:5">
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>43</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" hidden="1" spans="1:5">
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>44</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" hidden="1" spans="1:5">
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>46</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" hidden="1" spans="1:5">
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>48</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" hidden="1" spans="1:5">
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>50</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" hidden="1" spans="1:5">
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>52</v>
       </c>
@@ -2146,7 +2146,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" hidden="1" spans="1:5">
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>53</v>
       </c>
@@ -2163,7 +2163,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="30" hidden="1" spans="1:5">
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -2180,7 +2180,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" hidden="1" spans="1:5">
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
         <v>56</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" hidden="1" spans="1:5">
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
         <v>57</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="33" hidden="1" spans="1:5">
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>58</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="34" hidden="1" spans="1:5">
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
         <v>59</v>
       </c>
@@ -2248,7 +2248,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" hidden="1" spans="1:5">
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" hidden="1" spans="1:5">
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>61</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" hidden="1" spans="1:5">
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
         <v>62</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" hidden="1" spans="1:5">
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
         <v>64</v>
       </c>
@@ -2316,7 +2316,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" hidden="1" spans="1:5">
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
         <v>65</v>
       </c>
@@ -2333,7 +2333,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" hidden="1" spans="1:5">
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
         <v>66</v>
       </c>
@@ -2350,7 +2350,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="41" hidden="1" spans="1:5">
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
         <v>67</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="42" hidden="1" spans="1:5">
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
         <v>68</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" hidden="1" spans="1:5">
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
         <v>70</v>
       </c>
@@ -2401,7 +2401,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" hidden="1" spans="1:5">
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
         <v>71</v>
       </c>
@@ -2418,7 +2418,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="45" hidden="1" spans="1:5">
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
         <v>72</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="46" hidden="1" spans="1:5">
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
         <v>73</v>
       </c>
@@ -2452,7 +2452,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="47" hidden="1" spans="1:5">
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
         <v>74</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="48" hidden="1" spans="1:5">
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
         <v>75</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="49" hidden="1" spans="1:5">
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
         <v>77</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="50" hidden="1" spans="1:5">
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
         <v>78</v>
       </c>
@@ -2656,7 +2656,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" hidden="1" spans="1:5">
+    <row r="59" spans="1:5">
       <c r="A59" t="s">
         <v>88</v>
       </c>
@@ -2673,7 +2673,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="60" hidden="1" spans="1:5">
+    <row r="60" spans="1:5">
       <c r="A60" t="s">
         <v>90</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" hidden="1" spans="1:5">
+    <row r="61" spans="1:5">
       <c r="A61" t="s">
         <v>92</v>
       </c>
@@ -2707,7 +2707,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" hidden="1" spans="1:5">
+    <row r="62" spans="1:5">
       <c r="A62" t="s">
         <v>30</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" hidden="1" spans="1:5">
+    <row r="63" spans="1:5">
       <c r="A63" t="s">
         <v>95</v>
       </c>
@@ -2741,7 +2741,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="64" hidden="1" spans="1:5">
+    <row r="64" spans="1:5">
       <c r="A64" t="s">
         <v>97</v>
       </c>
@@ -2758,7 +2758,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="65" hidden="1" spans="1:5">
+    <row r="65" spans="1:5">
       <c r="A65" t="s">
         <v>99</v>
       </c>
@@ -2775,7 +2775,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="66" hidden="1" spans="1:5">
+    <row r="66" spans="1:5">
       <c r="A66" t="s">
         <v>101</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" hidden="1" spans="1:5">
+    <row r="67" spans="1:5">
       <c r="A67" t="s">
         <v>103</v>
       </c>
@@ -2809,7 +2809,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" hidden="1" spans="1:5">
+    <row r="68" spans="1:5">
       <c r="A68" t="s">
         <v>104</v>
       </c>
@@ -2826,7 +2826,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="69" hidden="1" spans="1:5">
+    <row r="69" spans="1:5">
       <c r="A69" t="s">
         <v>105</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" hidden="1" spans="1:5">
+    <row r="70" spans="1:5">
       <c r="A70" t="s">
         <v>106</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" hidden="1" spans="1:5">
+    <row r="71" spans="1:5">
       <c r="A71" t="s">
         <v>107</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="72" hidden="1" spans="1:5">
+    <row r="72" spans="1:5">
       <c r="A72" t="s">
         <v>52</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="73" hidden="1" spans="1:5">
+    <row r="73" spans="1:5">
       <c r="A73" t="s">
         <v>50</v>
       </c>
@@ -2911,7 +2911,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" hidden="1" spans="1:5">
+    <row r="74" spans="1:5">
       <c r="A74" t="s">
         <v>109</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="75" hidden="1" spans="1:5">
+    <row r="75" spans="1:5">
       <c r="A75" t="s">
         <v>110</v>
       </c>
@@ -2945,7 +2945,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="76" hidden="1" spans="1:5">
+    <row r="76" spans="1:5">
       <c r="A76" t="s">
         <v>111</v>
       </c>
@@ -2962,7 +2962,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="77" hidden="1" spans="1:5">
+    <row r="77" spans="1:5">
       <c r="A77" t="s">
         <v>78</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" hidden="1" spans="1:5">
+    <row r="78" spans="1:5">
       <c r="A78" t="s">
         <v>5</v>
       </c>
@@ -2996,7 +2996,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" hidden="1" spans="1:5">
+    <row r="79" spans="1:5">
       <c r="A79" t="s">
         <v>112</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="80" hidden="1" spans="1:5">
+    <row r="80" spans="1:5">
       <c r="A80" t="s">
         <v>114</v>
       </c>
@@ -3030,7 +3030,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="81" hidden="1" spans="1:5">
+    <row r="81" spans="1:5">
       <c r="A81" t="s">
         <v>115</v>
       </c>
@@ -3047,7 +3047,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="82" hidden="1" spans="1:5">
+    <row r="82" spans="1:5">
       <c r="A82" t="s">
         <v>116</v>
       </c>
@@ -3064,7 +3064,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="83" hidden="1" spans="1:5">
+    <row r="83" spans="1:5">
       <c r="A83" t="s">
         <v>117</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="84" hidden="1" spans="1:5">
+    <row r="84" spans="1:5">
       <c r="A84" t="s">
         <v>118</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" hidden="1" spans="1:5">
+    <row r="85" spans="1:5">
       <c r="A85" t="s">
         <v>119</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" hidden="1" spans="1:5">
+    <row r="86" spans="1:5">
       <c r="A86" t="s">
         <v>121</v>
       </c>
@@ -3132,7 +3132,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="87" hidden="1" spans="1:5">
+    <row r="87" spans="1:5">
       <c r="A87" t="s">
         <v>122</v>
       </c>
@@ -3149,7 +3149,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" hidden="1" spans="1:5">
+    <row r="88" spans="1:5">
       <c r="A88" t="s">
         <v>123</v>
       </c>
@@ -3166,7 +3166,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="89" hidden="1" spans="1:5">
+    <row r="89" spans="1:5">
       <c r="A89" t="s">
         <v>124</v>
       </c>
@@ -3183,7 +3183,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="90" hidden="1" spans="1:5">
+    <row r="90" spans="1:5">
       <c r="A90" t="s">
         <v>126</v>
       </c>
@@ -3200,7 +3200,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" hidden="1" spans="1:5">
+    <row r="91" spans="1:5">
       <c r="A91" t="s">
         <v>127</v>
       </c>
@@ -3217,7 +3217,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" hidden="1" spans="1:5">
+    <row r="92" spans="1:5">
       <c r="A92" t="s">
         <v>128</v>
       </c>
@@ -3234,7 +3234,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="93" hidden="1" spans="1:5">
+    <row r="93" spans="1:5">
       <c r="A93" t="s">
         <v>129</v>
       </c>
@@ -3251,7 +3251,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="94" hidden="1" spans="1:5">
+    <row r="94" spans="1:5">
       <c r="A94" t="s">
         <v>131</v>
       </c>
@@ -3268,7 +3268,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" hidden="1" spans="1:5">
+    <row r="95" spans="1:5">
       <c r="A95" t="s">
         <v>132</v>
       </c>
@@ -3285,7 +3285,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="96" hidden="1" spans="1:5">
+    <row r="96" spans="1:5">
       <c r="A96" t="s">
         <v>133</v>
       </c>
@@ -3302,7 +3302,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="97" hidden="1" spans="1:5">
+    <row r="97" spans="1:5">
       <c r="A97" t="s">
         <v>134</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="98" hidden="1" spans="1:5">
+    <row r="98" spans="1:5">
       <c r="A98" t="s">
         <v>109</v>
       </c>
@@ -3336,7 +3336,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="99" hidden="1" spans="1:5">
+    <row r="99" spans="1:5">
       <c r="A99" t="s">
         <v>110</v>
       </c>
@@ -3353,7 +3353,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="100" hidden="1" spans="1:5">
+    <row r="100" spans="1:5">
       <c r="A100" t="s">
         <v>137</v>
       </c>
@@ -3370,7 +3370,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="101" hidden="1" spans="1:5">
+    <row r="101" spans="1:5">
       <c r="A101" t="s">
         <v>111</v>
       </c>
@@ -3387,7 +3387,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="102" hidden="1" spans="1:5">
+    <row r="102" spans="1:5">
       <c r="A102" t="s">
         <v>119</v>
       </c>
@@ -3404,7 +3404,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" hidden="1" spans="1:5">
+    <row r="103" spans="1:5">
       <c r="A103" t="s">
         <v>123</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="104" hidden="1" spans="1:5">
+    <row r="104" spans="1:5">
       <c r="A104" t="s">
         <v>140</v>
       </c>
@@ -3438,7 +3438,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" hidden="1" spans="1:5">
+    <row r="105" spans="1:5">
       <c r="A105" t="s">
         <v>141</v>
       </c>
@@ -3455,7 +3455,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="106" hidden="1" spans="1:5">
+    <row r="106" spans="1:5">
       <c r="A106" t="s">
         <v>143</v>
       </c>
@@ -3472,7 +3472,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" hidden="1" spans="1:5">
+    <row r="107" spans="1:5">
       <c r="A107" t="s">
         <v>144</v>
       </c>
@@ -3489,7 +3489,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="108" hidden="1" spans="1:5">
+    <row r="108" spans="1:5">
       <c r="A108" t="s">
         <v>146</v>
       </c>
@@ -3506,7 +3506,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" hidden="1" spans="1:5">
+    <row r="109" spans="1:5">
       <c r="A109" t="s">
         <v>147</v>
       </c>
@@ -3523,7 +3523,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" hidden="1" spans="1:5">
+    <row r="110" spans="1:5">
       <c r="A110" t="s">
         <v>149</v>
       </c>
@@ -3540,7 +3540,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="111" hidden="1" spans="1:5">
+    <row r="111" spans="1:5">
       <c r="A111" t="s">
         <v>34</v>
       </c>
@@ -3557,7 +3557,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="112" hidden="1" spans="1:5">
+    <row r="112" spans="1:5">
       <c r="A112" t="s">
         <v>52</v>
       </c>
@@ -3574,7 +3574,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="113" hidden="1" spans="1:5">
+    <row r="113" spans="1:5">
       <c r="A113" t="s">
         <v>30</v>
       </c>
@@ -3591,7 +3591,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="114" hidden="1" spans="1:5">
+    <row r="114" spans="1:5">
       <c r="A114" t="s">
         <v>53</v>
       </c>
@@ -3608,7 +3608,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="115" hidden="1" spans="1:5">
+    <row r="115" spans="1:5">
       <c r="A115" t="s">
         <v>151</v>
       </c>
@@ -3625,7 +3625,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="116" hidden="1" spans="1:5">
+    <row r="116" spans="1:5">
       <c r="A116" t="s">
         <v>153</v>
       </c>
@@ -3642,7 +3642,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="117" hidden="1" spans="1:5">
+    <row r="117" spans="1:5">
       <c r="A117" t="s">
         <v>64</v>
       </c>
@@ -3659,7 +3659,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="118" hidden="1" spans="1:5">
+    <row r="118" spans="1:5">
       <c r="A118" t="s">
         <v>154</v>
       </c>
@@ -3676,7 +3676,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" hidden="1" spans="1:5">
+    <row r="119" spans="1:5">
       <c r="A119" t="s">
         <v>155</v>
       </c>
@@ -3693,7 +3693,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="120" hidden="1" spans="1:5">
+    <row r="120" spans="1:5">
       <c r="A120" t="s">
         <v>156</v>
       </c>
@@ -3710,7 +3710,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="121" hidden="1" spans="1:5">
+    <row r="121" spans="1:5">
       <c r="A121" t="s">
         <v>157</v>
       </c>
@@ -3727,7 +3727,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="122" hidden="1" spans="1:5">
+    <row r="122" spans="1:5">
       <c r="A122" t="s">
         <v>159</v>
       </c>
@@ -3744,7 +3744,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="123" hidden="1" spans="1:5">
+    <row r="123" spans="1:5">
       <c r="A123" t="s">
         <v>160</v>
       </c>
@@ -3761,7 +3761,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" hidden="1" spans="1:5">
+    <row r="124" spans="1:5">
       <c r="A124" t="s">
         <v>161</v>
       </c>
@@ -3778,7 +3778,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="125" hidden="1" spans="1:5">
+    <row r="125" spans="1:5">
       <c r="A125" t="s">
         <v>162</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="126" hidden="1" spans="1:5">
+    <row r="126" spans="1:5">
       <c r="A126" t="s">
         <v>164</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="127" hidden="1" spans="1:5">
+    <row r="127" spans="1:5">
       <c r="A127" t="s">
         <v>165</v>
       </c>
@@ -3829,7 +3829,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="128" hidden="1" spans="1:5">
+    <row r="128" spans="1:5">
       <c r="A128" t="s">
         <v>166</v>
       </c>
@@ -3846,7 +3846,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="129" hidden="1" spans="1:5">
+    <row r="129" spans="1:5">
       <c r="A129" t="s">
         <v>167</v>
       </c>
@@ -3863,7 +3863,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="130" hidden="1" spans="1:5">
+    <row r="130" spans="1:5">
       <c r="A130" t="s">
         <v>168</v>
       </c>
@@ -3880,7 +3880,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="131" hidden="1" spans="1:5">
+    <row r="131" spans="1:5">
       <c r="A131" t="s">
         <v>169</v>
       </c>
@@ -3897,7 +3897,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="132" hidden="1" spans="1:5">
+    <row r="132" spans="1:5">
       <c r="A132" t="s">
         <v>171</v>
       </c>
@@ -3914,7 +3914,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="133" hidden="1" spans="1:5">
+    <row r="133" spans="1:5">
       <c r="A133" t="s">
         <v>173</v>
       </c>
@@ -3931,7 +3931,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" hidden="1" spans="1:5">
+    <row r="134" spans="1:5">
       <c r="A134" t="s">
         <v>174</v>
       </c>
@@ -3948,7 +3948,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="135" hidden="1" spans="1:5">
+    <row r="135" spans="1:5">
       <c r="A135" t="s">
         <v>175</v>
       </c>
@@ -3965,7 +3965,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="136" hidden="1" spans="1:5">
+    <row r="136" spans="1:5">
       <c r="A136" t="s">
         <v>177</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="137" hidden="1" spans="1:5">
+    <row r="137" spans="1:5">
       <c r="A137" t="s">
         <v>178</v>
       </c>
@@ -3999,7 +3999,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="138" hidden="1" spans="1:5">
+    <row r="138" spans="1:5">
       <c r="A138" t="s">
         <v>179</v>
       </c>
@@ -4016,7 +4016,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="139" hidden="1" spans="1:5">
+    <row r="139" spans="1:5">
       <c r="A139" t="s">
         <v>77</v>
       </c>
@@ -4033,7 +4033,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="140" hidden="1" spans="1:5">
+    <row r="140" spans="1:5">
       <c r="A140" t="s">
         <v>36</v>
       </c>
@@ -4050,7 +4050,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="141" hidden="1" spans="1:5">
+    <row r="141" spans="1:5">
       <c r="A141" t="s">
         <v>180</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="142" hidden="1" spans="1:5">
+    <row r="142" spans="1:5">
       <c r="A142" t="s">
         <v>78</v>
       </c>
@@ -4084,7 +4084,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="143" hidden="1" spans="1:5">
+    <row r="143" spans="1:5">
       <c r="A143" t="s">
         <v>50</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="144" hidden="1" spans="1:5">
+    <row r="144" spans="1:5">
       <c r="A144" t="s">
         <v>58</v>
       </c>
@@ -4118,7 +4118,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="145" hidden="1" spans="1:5">
+    <row r="145" spans="1:5">
       <c r="A145" t="s">
         <v>141</v>
       </c>
@@ -4135,7 +4135,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="146" hidden="1" spans="1:5">
+    <row r="146" spans="1:5">
       <c r="A146" t="s">
         <v>181</v>
       </c>
@@ -4152,7 +4152,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="147" hidden="1" spans="1:5">
+    <row r="147" spans="1:5">
       <c r="A147" t="s">
         <v>122</v>
       </c>
@@ -4169,7 +4169,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="148" hidden="1" spans="1:5">
+    <row r="148" spans="1:5">
       <c r="A148" t="s">
         <v>119</v>
       </c>
@@ -4186,7 +4186,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="149" hidden="1" spans="1:5">
+    <row r="149" spans="1:5">
       <c r="A149" t="s">
         <v>123</v>
       </c>
@@ -4203,7 +4203,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="150" hidden="1" spans="1:5">
+    <row r="150" spans="1:5">
       <c r="A150" t="s">
         <v>101</v>
       </c>
@@ -4220,7 +4220,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="151" hidden="1" spans="1:5">
+    <row r="151" spans="1:5">
       <c r="A151" t="s">
         <v>182</v>
       </c>
@@ -4237,7 +4237,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="152" hidden="1" spans="1:5">
+    <row r="152" spans="1:5">
       <c r="A152" t="s">
         <v>183</v>
       </c>
@@ -4254,7 +4254,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="153" hidden="1" spans="1:5">
+    <row r="153" spans="1:5">
       <c r="A153" t="s">
         <v>157</v>
       </c>
@@ -4271,7 +4271,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="154" hidden="1" spans="1:5">
+    <row r="154" spans="1:5">
       <c r="A154" t="s">
         <v>184</v>
       </c>
@@ -4288,7 +4288,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="155" hidden="1" spans="1:5">
+    <row r="155" spans="1:5">
       <c r="A155" t="s">
         <v>127</v>
       </c>
@@ -4305,7 +4305,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156" hidden="1" spans="1:5">
+    <row r="156" spans="1:5">
       <c r="A156" t="s">
         <v>185</v>
       </c>
@@ -4322,7 +4322,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" hidden="1" spans="1:5">
+    <row r="157" spans="1:5">
       <c r="A157" t="s">
         <v>186</v>
       </c>
@@ -4339,7 +4339,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="158" hidden="1" spans="1:5">
+    <row r="158" spans="1:5">
       <c r="A158" t="s">
         <v>149</v>
       </c>
@@ -4356,7 +4356,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="159" hidden="1" spans="1:5">
+    <row r="159" spans="1:5">
       <c r="A159" t="s">
         <v>187</v>
       </c>
@@ -4373,7 +4373,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="160" hidden="1" spans="1:5">
+    <row r="160" spans="1:5">
       <c r="A160" t="s">
         <v>188</v>
       </c>
@@ -4390,7 +4390,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="161" hidden="1" spans="1:5">
+    <row r="161" spans="1:5">
       <c r="A161" t="s">
         <v>189</v>
       </c>
@@ -4407,7 +4407,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="162" hidden="1" spans="1:5">
+    <row r="162" spans="1:5">
       <c r="A162" t="s">
         <v>190</v>
       </c>
@@ -4424,7 +4424,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="163" hidden="1" spans="1:5">
+    <row r="163" spans="1:5">
       <c r="A163" t="s">
         <v>191</v>
       </c>
@@ -4441,7 +4441,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="164" hidden="1" spans="1:5">
+    <row r="164" spans="1:5">
       <c r="A164" t="s">
         <v>192</v>
       </c>
@@ -4458,7 +4458,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" hidden="1" spans="1:5">
+    <row r="165" spans="1:5">
       <c r="A165" t="s">
         <v>193</v>
       </c>
@@ -4475,7 +4475,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="166" hidden="1" spans="1:5">
+    <row r="166" spans="1:5">
       <c r="A166" t="s">
         <v>140</v>
       </c>
@@ -4492,7 +4492,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="167" hidden="1" spans="1:5">
+    <row r="167" spans="1:5">
       <c r="A167" t="s">
         <v>126</v>
       </c>
@@ -4509,7 +4509,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="168" hidden="1" spans="1:5">
+    <row r="168" spans="1:5">
       <c r="A168" t="s">
         <v>131</v>
       </c>
@@ -4526,7 +4526,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="169" hidden="1" spans="1:5">
+    <row r="169" spans="1:5">
       <c r="A169" t="s">
         <v>194</v>
       </c>
@@ -4543,7 +4543,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="170" hidden="1" spans="1:5">
+    <row r="170" spans="1:5">
       <c r="A170" t="s">
         <v>196</v>
       </c>
@@ -4560,7 +4560,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="171" hidden="1" spans="1:5">
+    <row r="171" spans="1:5">
       <c r="A171" t="s">
         <v>166</v>
       </c>
@@ -4577,7 +4577,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="172" hidden="1" spans="1:5">
+    <row r="172" spans="1:5">
       <c r="A172" t="s">
         <v>198</v>
       </c>
@@ -4594,7 +4594,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="173" hidden="1" spans="1:5">
+    <row r="173" spans="1:5">
       <c r="A173" t="s">
         <v>199</v>
       </c>
@@ -4611,7 +4611,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="174" hidden="1" spans="1:5">
+    <row r="174" spans="1:5">
       <c r="A174" t="s">
         <v>200</v>
       </c>
@@ -4628,7 +4628,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="175" hidden="1" spans="1:5">
+    <row r="175" spans="1:5">
       <c r="A175" t="s">
         <v>201</v>
       </c>
@@ -4645,7 +4645,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="176" hidden="1" spans="1:5">
+    <row r="176" spans="1:5">
       <c r="A176" t="s">
         <v>116</v>
       </c>
@@ -4662,7 +4662,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="177" hidden="1" spans="1:5">
+    <row r="177" spans="1:5">
       <c r="A177" t="s">
         <v>117</v>
       </c>
@@ -4679,7 +4679,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="178" hidden="1" spans="1:5">
+    <row r="178" spans="1:5">
       <c r="A178" t="s">
         <v>202</v>
       </c>
@@ -4696,7 +4696,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="179" hidden="1" spans="1:5">
+    <row r="179" spans="1:5">
       <c r="A179" t="s">
         <v>203</v>
       </c>
@@ -4713,7 +4713,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="180" hidden="1" spans="1:5">
+    <row r="180" spans="1:5">
       <c r="A180" t="s">
         <v>204</v>
       </c>
@@ -4730,7 +4730,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="181" hidden="1" spans="1:5">
+    <row r="181" spans="1:5">
       <c r="A181" t="s">
         <v>205</v>
       </c>
@@ -4747,7 +4747,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="182" hidden="1" spans="1:5">
+    <row r="182" spans="1:5">
       <c r="A182" t="s">
         <v>109</v>
       </c>
@@ -4764,7 +4764,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="183" hidden="1" spans="1:5">
+    <row r="183" spans="1:5">
       <c r="A183" t="s">
         <v>206</v>
       </c>
@@ -4781,7 +4781,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="184" hidden="1" spans="1:5">
+    <row r="184" spans="1:5">
       <c r="A184" t="s">
         <v>207</v>
       </c>
@@ -4798,7 +4798,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="185" hidden="1" spans="1:5">
+    <row r="185" spans="1:5">
       <c r="A185" t="s">
         <v>208</v>
       </c>
@@ -4815,7 +4815,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="186" hidden="1" spans="1:5">
+    <row r="186" spans="1:5">
       <c r="A186" t="s">
         <v>209</v>
       </c>
@@ -4832,7 +4832,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="187" hidden="1" spans="1:5">
+    <row r="187" spans="1:5">
       <c r="A187" t="s">
         <v>210</v>
       </c>
@@ -4849,7 +4849,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="188" hidden="1" spans="1:5">
+    <row r="188" spans="1:5">
       <c r="A188" t="s">
         <v>211</v>
       </c>
@@ -4866,7 +4866,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="189" hidden="1" spans="1:5">
+    <row r="189" spans="1:5">
       <c r="A189" t="s">
         <v>175</v>
       </c>
@@ -4885,11 +4885,6 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E189" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Breakout"/>
-      </filters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
   <dataValidations count="1">
